--- a/main/ig/StructureDefinition-ror-healthcareservice.xlsx
+++ b/main/ig/StructureDefinition-ror-healthcareservice.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-30T10:12:59+00:00</t>
+    <t>2026-03-09T13:22:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-ror-healthcareservice.xlsx
+++ b/main/ig/StructureDefinition-ror-healthcareservice.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-09T13:22:43+00:00</t>
+    <t>2026-03-17T11:12:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-ror-healthcareservice.xlsx
+++ b/main/ig/StructureDefinition-ror-healthcareservice.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-17T11:12:47+00:00</t>
+    <t>2026-03-23T15:20:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-ror-healthcareservice.xlsx
+++ b/main/ig/StructureDefinition-ror-healthcareservice.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-23T15:20:38+00:00</t>
+    <t>2026-03-24T09:51:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-ror-healthcareservice.xlsx
+++ b/main/ig/StructureDefinition-ror-healthcareservice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.0-snapshot-1</t>
+    <t>0.7.0-snapshot-2</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-24T09:51:35+00:00</t>
+    <t>2026-03-24T10:30:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-ror-healthcareservice.xlsx
+++ b/main/ig/StructureDefinition-ror-healthcareservice.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T08:33:49+00:00</t>
+    <t>2026-04-29T13:16:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-ror-healthcareservice.xlsx
+++ b/main/ig/StructureDefinition-ror-healthcareservice.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.0-snapshot-2</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T13:16:27+00:00</t>
+    <t>2026-04-29T15:21:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-ror-healthcareservice.xlsx
+++ b/main/ig/StructureDefinition-ror-healthcareservice.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T15:21:13+00:00</t>
+    <t>2026-04-29T15:21:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-ror-healthcareservice.xlsx
+++ b/main/ig/StructureDefinition-ror-healthcareservice.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T15:21:33+00:00</t>
+    <t>2026-07-23T07:54:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -446,7 +446,7 @@
     <t>HealthcareService.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -484,7 +484,7 @@
     <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
   </si>
   <si>
     <t>Meta.security</t>
@@ -511,7 +511,7 @@
     <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
+    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
   </si>
   <si>
     <t>Slicing pour gérer le code région définissant la région source des données</t>
@@ -572,7 +572,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -1192,7 +1192,7 @@
     <t>A specialty that a healthcare service may provide.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/c80-practice-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/c80-practice-codes|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">value:coding.system}
@@ -1558,7 +1558,7 @@
     <t>The provision means being commissioned by, contractually obliged or financially sourced. Types of costings that may apply to this healthcare service, such if the service may be available for free, some discounts available, or fees apply.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/service-provision-conditions</t>
+    <t>http://hl7.org/fhir/ValueSet/service-provision-conditions|4.0.1</t>
   </si>
   <si>
     <t>.actrelationship[typeCode=PRCN].observation[moodCode=EVN.CRT]</t>
@@ -1642,7 +1642,7 @@
     <t>Government or local programs that this service applies to.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/program</t>
+    <t>http://hl7.org/fhir/ValueSet/program|4.0.1</t>
   </si>
   <si>
     <t>.actrelationship[typeCode=PERT].observation</t>
@@ -2157,7 +2157,7 @@
     <t>The methods of referral can be used when referring to a specific HealthCareService resource.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/service-referral-method</t>
+    <t>http://hl7.org/fhir/ValueSet/service-referral-method|4.0.1</t>
   </si>
   <si>
     <t>HealthcareService.appointmentRequired</t>
@@ -2449,7 +2449,7 @@
     <t>HealthcareService.endpoint</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Endpoint)
+    <t xml:space="preserve">Reference(Endpoint|4.0.1)
 </t>
   </si>
   <si>
@@ -2777,15 +2777,15 @@
   <dimension ref="A1:AM214"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="100.6484375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="50.01953125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="46.02734375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="86.2890625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="42.8828125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="39.4609375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2796,25 +2796,25 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="98.61328125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="117.69140625" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="84.06640625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="69.203125" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="49.1328125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="84.54296875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="100.8984375" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="72.0703125" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="59.33203125" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="42.125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="61.59375" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="72.5234375" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="36.91796875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="52.8046875" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="62.17578125" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="31.65234375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3596,7 +3596,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="8" hidden="true">
+    <row r="8">
       <c r="A8" t="s" s="2">
         <v>124</v>
       </c>
@@ -4151,7 +4151,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="13" hidden="true">
+    <row r="13">
       <c r="A13" t="s" s="2">
         <v>162</v>
       </c>
@@ -4815,7 +4815,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="19" hidden="true">
+    <row r="19">
       <c r="A19" t="s" s="2">
         <v>201</v>
       </c>
@@ -6458,7 +6458,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
         <v>245</v>
       </c>
@@ -6569,7 +6569,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="35" hidden="true">
+    <row r="35">
       <c r="A35" t="s" s="2">
         <v>251</v>
       </c>
@@ -6680,7 +6680,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="36" hidden="true">
+    <row r="36">
       <c r="A36" t="s" s="2">
         <v>257</v>
       </c>
@@ -6791,7 +6791,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="37" hidden="true">
+    <row r="37">
       <c r="A37" t="s" s="2">
         <v>263</v>
       </c>
@@ -6902,7 +6902,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="38" hidden="true">
+    <row r="38">
       <c r="A38" t="s" s="2">
         <v>269</v>
       </c>
@@ -9429,7 +9429,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="61" hidden="true">
+    <row r="61">
       <c r="A61" t="s" s="2">
         <v>313</v>
       </c>
@@ -9540,7 +9540,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="62" hidden="true">
+    <row r="62">
       <c r="A62" t="s" s="2">
         <v>319</v>
       </c>
@@ -9764,7 +9764,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="64" hidden="true">
+    <row r="64">
       <c r="A64" t="s" s="2">
         <v>330</v>
       </c>
@@ -9986,7 +9986,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="66" hidden="true">
+    <row r="66">
       <c r="A66" t="s" s="2">
         <v>346</v>
       </c>
@@ -10097,7 +10097,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="67" hidden="true">
+    <row r="67">
       <c r="A67" t="s" s="2">
         <v>354</v>
       </c>
@@ -10206,7 +10206,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="68" hidden="true">
+    <row r="68">
       <c r="A68" t="s" s="2">
         <v>363</v>
       </c>
@@ -10424,7 +10424,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="70" hidden="true">
+    <row r="70">
       <c r="A70" t="s" s="2">
         <v>377</v>
       </c>
@@ -10535,7 +10535,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="71" hidden="true">
+    <row r="71">
       <c r="A71" t="s" s="2">
         <v>382</v>
       </c>
@@ -10646,7 +10646,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="72" hidden="true">
+    <row r="72">
       <c r="A72" t="s" s="2">
         <v>387</v>
       </c>
@@ -10757,7 +10757,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="73" hidden="true">
+    <row r="73">
       <c r="A73" t="s" s="2">
         <v>395</v>
       </c>
@@ -11530,7 +11530,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="80" hidden="true">
+    <row r="80">
       <c r="A80" t="s" s="2">
         <v>430</v>
       </c>
@@ -11641,7 +11641,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="81" hidden="true">
+    <row r="81">
       <c r="A81" t="s" s="2">
         <v>435</v>
       </c>
@@ -11752,7 +11752,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="82" hidden="true">
+    <row r="82">
       <c r="A82" t="s" s="2">
         <v>440</v>
       </c>
@@ -11974,7 +11974,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="84" hidden="true">
+    <row r="84">
       <c r="A84" t="s" s="2">
         <v>453</v>
       </c>
@@ -13748,7 +13748,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="100" hidden="true">
+    <row r="100">
       <c r="A100" t="s" s="2">
         <v>529</v>
       </c>
@@ -14085,7 +14085,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="103" hidden="true">
+    <row r="103">
       <c r="A103" t="s" s="2">
         <v>548</v>
       </c>
@@ -14416,7 +14416,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="106" hidden="true">
+    <row r="106">
       <c r="A106" t="s" s="2">
         <v>555</v>
       </c>
@@ -14753,7 +14753,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="109" hidden="true">
+    <row r="109">
       <c r="A109" t="s" s="2">
         <v>558</v>
       </c>
@@ -15084,7 +15084,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="112" hidden="true">
+    <row r="112">
       <c r="A112" t="s" s="2">
         <v>565</v>
       </c>
@@ -15421,7 +15421,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="115" hidden="true">
+    <row r="115">
       <c r="A115" t="s" s="2">
         <v>568</v>
       </c>
@@ -15752,7 +15752,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="118" hidden="true">
+    <row r="118">
       <c r="A118" t="s" s="2">
         <v>575</v>
       </c>
@@ -16089,7 +16089,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="121" hidden="true">
+    <row r="121">
       <c r="A121" t="s" s="2">
         <v>578</v>
       </c>
@@ -16420,7 +16420,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="124" hidden="true">
+    <row r="124">
       <c r="A124" t="s" s="2">
         <v>585</v>
       </c>
@@ -16757,7 +16757,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="127" hidden="true">
+    <row r="127">
       <c r="A127" t="s" s="2">
         <v>588</v>
       </c>
@@ -16993,10 +16993,10 @@
         <v>85</v>
       </c>
       <c r="G129" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H129" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I129" t="s" s="2">
         <v>75</v>
@@ -17005,13 +17005,13 @@
         <v>75</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>531</v>
+        <v>110</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>532</v>
+        <v>198</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>533</v>
+        <v>199</v>
       </c>
       <c r="N129" s="2"/>
       <c r="O129" s="2"/>
@@ -17086,7 +17086,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="130" hidden="true">
+    <row r="130">
       <c r="A130" t="s" s="2">
         <v>595</v>
       </c>
@@ -17859,7 +17859,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="137" hidden="true">
+    <row r="137">
       <c r="A137" t="s" s="2">
         <v>608</v>
       </c>
@@ -18095,10 +18095,10 @@
         <v>85</v>
       </c>
       <c r="G139" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H139" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I139" t="s" s="2">
         <v>75</v>
@@ -18107,13 +18107,13 @@
         <v>75</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>531</v>
+        <v>110</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>532</v>
+        <v>198</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>533</v>
+        <v>199</v>
       </c>
       <c r="N139" s="2"/>
       <c r="O139" s="2"/>
@@ -18188,7 +18188,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="140" hidden="true">
+    <row r="140">
       <c r="A140" t="s" s="2">
         <v>614</v>
       </c>
@@ -18961,7 +18961,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="147" hidden="true">
+    <row r="147">
       <c r="A147" t="s" s="2">
         <v>621</v>
       </c>
@@ -19292,7 +19292,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="150" hidden="true">
+    <row r="150">
       <c r="A150" t="s" s="2">
         <v>628</v>
       </c>
@@ -19629,7 +19629,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="153" hidden="true">
+    <row r="153">
       <c r="A153" t="s" s="2">
         <v>631</v>
       </c>
@@ -19960,7 +19960,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="156" hidden="true">
+    <row r="156">
       <c r="A156" t="s" s="2">
         <v>638</v>
       </c>
@@ -20297,7 +20297,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="159" hidden="true">
+    <row r="159">
       <c r="A159" t="s" s="2">
         <v>641</v>
       </c>
@@ -20628,7 +20628,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="162" hidden="true">
+    <row r="162">
       <c r="A162" t="s" s="2">
         <v>648</v>
       </c>
@@ -20965,7 +20965,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="165" hidden="true">
+    <row r="165">
       <c r="A165" t="s" s="2">
         <v>651</v>
       </c>
@@ -21296,7 +21296,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="168" hidden="true">
+    <row r="168">
       <c r="A168" t="s" s="2">
         <v>658</v>
       </c>
@@ -21633,7 +21633,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="171" hidden="true">
+    <row r="171">
       <c r="A171" t="s" s="2">
         <v>661</v>
       </c>
@@ -21964,7 +21964,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="174" hidden="true">
+    <row r="174">
       <c r="A174" t="s" s="2">
         <v>668</v>
       </c>
@@ -22301,7 +22301,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="177" hidden="true">
+    <row r="177">
       <c r="A177" t="s" s="2">
         <v>671</v>
       </c>
@@ -22632,7 +22632,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="180" hidden="true">
+    <row r="180">
       <c r="A180" t="s" s="2">
         <v>678</v>
       </c>
@@ -23300,7 +23300,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="186" hidden="true">
+    <row r="186">
       <c r="A186" t="s" s="2">
         <v>694</v>
       </c>
@@ -23631,7 +23631,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="189" hidden="true">
+    <row r="189">
       <c r="A189" t="s" s="2">
         <v>702</v>
       </c>
@@ -23742,7 +23742,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="190" hidden="true">
+    <row r="190">
       <c r="A190" t="s" s="2">
         <v>707</v>
       </c>
@@ -23853,7 +23853,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="191" hidden="true">
+    <row r="191">
       <c r="A191" t="s" s="2">
         <v>712</v>
       </c>
@@ -24297,7 +24297,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="195" hidden="true">
+    <row r="195">
       <c r="A195" t="s" s="2">
         <v>726</v>
       </c>
@@ -24408,7 +24408,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="196" hidden="true">
+    <row r="196">
       <c r="A196" t="s" s="2">
         <v>732</v>
       </c>
@@ -25181,7 +25181,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="203" hidden="true">
+    <row r="203">
       <c r="A203" t="s" s="2">
         <v>749</v>
       </c>
@@ -26515,12 +26515,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AM214">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>

--- a/main/ig/StructureDefinition-ror-healthcareservice.xlsx
+++ b/main/ig/StructureDefinition-ror-healthcareservice.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T07:54:45+00:00</t>
+    <t>2026-07-23T08:00:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-ror-healthcareservice.xlsx
+++ b/main/ig/StructureDefinition-ror-healthcareservice.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T08:00:07+00:00</t>
+    <t>2026-07-23T08:13:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
